--- a/Vf/TABLE_4_5/Table_5_PanelD_MIDAS.xlsx
+++ b/Vf/TABLE_4_5/Table_5_PanelD_MIDAS.xlsx
@@ -484,13 +484,13 @@
         <v>1.080392546859021</v>
       </c>
       <c r="C4" t="n">
-        <v>1.115303339479359</v>
+        <v>1.115159786817494</v>
       </c>
       <c r="D4" t="n">
-        <v>1.13195120529391</v>
+        <v>1.131959056341275</v>
       </c>
       <c r="E4" t="n">
-        <v>1.233636052886394</v>
+        <v>1.23362621572914</v>
       </c>
     </row>
     <row r="5">
@@ -515,10 +515,10 @@
         <v>0.95</v>
       </c>
       <c r="B6" t="n">
-        <v>1.190387160660586</v>
+        <v>1.186753117367767</v>
       </c>
       <c r="C6" t="n">
-        <v>1.288393548933058</v>
+        <v>1.287664991273022</v>
       </c>
       <c r="D6" t="n">
         <v>1.29568626346573</v>
